--- a/Outputs/PtX_demand_HR.xlsx
+++ b/Outputs/PtX_demand_HR.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,32 +488,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2030</v>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>0.0001494315686924134</v>
-      </c>
+      <c r="C2" t="n">
+        <v>0.0005147853254422725</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0008421026685774733</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0007836259586892497</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>3.276239403201783e-10</v>
-      </c>
-      <c r="I2" t="n">
-        <v>7.140807280321497e-05</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -522,26 +522,30 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.0001494315686924134</v>
+      </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>3.276239403201783e-10</v>
+      </c>
+      <c r="I3" t="n">
+        <v>7.140807280321497e-05</v>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2030</v>
       </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="n">
-        <v>0.006923909833759821</v>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -553,14 +557,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2030</v>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>0.006923909833759821</v>
+      </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -572,7 +578,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -580,24 +586,18 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
-        <v>0.0002821052278641759</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4.329939095298977e-05</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>1.437804029318445e-05</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -605,14 +605,16 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>0.0002821052278641759</v>
+      </c>
       <c r="F7" t="n">
-        <v>0.0005753006392829026</v>
+        <v>4.329939095298977e-05</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>5.54567252492964e-05</v>
+        <v>1.437804029318445e-05</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -620,7 +622,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -629,17 +631,21 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.0005753006392829026</v>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>5.54567252492964e-05</v>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -648,29 +654,17 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>0.002690377581549762</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.580819324323321e-05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0007394122816492519</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0026028361683547</v>
-      </c>
-      <c r="J9" t="n">
-        <v>6.745244893490615e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.001251833395232873</v>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -680,28 +674,28 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>0.0268422477686697</v>
+        <v>0.002690377581549762</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0001113324693366</v>
+        <v>1.580819324323321e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0067299634888682</v>
+        <v>0.0007394122816492519</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0165521734152812</v>
+        <v>0.0026028361683547</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0004082898153107</v>
+        <v>6.745244893490615e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0120421763211259</v>
+        <v>0.001251833395232873</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -709,20 +703,30 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="n">
-        <v>0.0006539468626333447</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0.0268422477686697</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0001113324693366</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0067299634888682</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.0165521734152812</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0004082898153107</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0120421763211259</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -731,7 +735,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>0.0007197498252196999</v>
+        <v>0.0006539468626333447</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -743,96 +747,100 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2030</v>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" t="n">
-        <v>0.006923909833759821</v>
-      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.001655801915717221</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.03030065694914777</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.0001271406625798332</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.007469376098141392</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.0192962524219816</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.0004757422642456062</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.01329400971635877</v>
-      </c>
+        <v>0.009016695477754882</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="n">
-        <v>0.0007195038800017403</v>
-      </c>
+      <c r="E14" t="n">
+        <v>0.0007197498252196999</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
-        <v>2.742574243668193e-08</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.0001062439896573091</v>
-      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2040</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+        <v>2030</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0005147853254422725</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.007766012502337294</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.01145612335216135</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.03030065694914777</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0001271406625798332</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.007469376098141392</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.0192962524219816</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.0004757422642456062</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.01329400971635877</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2040</v>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>0.0005010576921071216</v>
+      </c>
       <c r="D16" t="n">
-        <v>0.006922555424109728</v>
-      </c>
-      <c r="E16" t="inlineStr"/>
+        <v>0.0006819866733664854</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0007921452568742928</v>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -843,7 +851,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -853,12 +861,14 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>2.609391163834029e-10</v>
+        <v>0.0007195038800017403</v>
       </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>2.742574243668193e-08</v>
+      </c>
       <c r="I17" t="n">
-        <v>3.400322149121844e-11</v>
+        <v>0.0001062439896573091</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -866,7 +876,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -874,47 +884,39 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="n">
-        <v>0.000985768159613077</v>
-      </c>
-      <c r="F18" t="n">
-        <v>5.390726543100483e-05</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="n">
-        <v>2.342761718180076e-05</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2040</v>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>0.006922555424109728</v>
+      </c>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="n">
-        <v>0.0003096724302784673</v>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="n">
-        <v>5.915836569318424e-05</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -923,17 +925,21 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>2.609391163834029e-10</v>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>3.400322149121844e-11</v>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -941,30 +947,24 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>0.000985768159613077</v>
+      </c>
       <c r="F21" t="n">
-        <v>0.001159179307294367</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2.576996294045299e-05</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.0009093343726798519</v>
-      </c>
+        <v>5.390726543100483e-05</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.001735827221761</v>
-      </c>
-      <c r="J21" t="n">
-        <v>8.194377803387662e-05</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.0014314440640491</v>
-      </c>
+        <v>2.342761718180076e-05</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -974,28 +974,20 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>0.007325348721515</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.000119688594305</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.006349186668053</v>
-      </c>
+        <v>0.0003096724302784673</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.007474822992653</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.0003623206834181</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.0116305293046029</v>
-      </c>
+        <v>5.915836569318424e-05</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1003,9 +995,7 @@
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
-        <v>0.0006425771149646283</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -1016,7 +1006,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1024,88 +1014,92 @@
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="n">
-        <v>0.002659399754462571</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0.001159179307294367</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.576996294045299e-05</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.0009093343726798519</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.001735827221761</v>
+      </c>
+      <c r="J24" t="n">
+        <v>8.194377803387662e-05</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.0014314440640491</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2040</v>
       </c>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" t="n">
-        <v>0.006922555424109728</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.004287745029040276</v>
-      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>0.009567611865459695</v>
+        <v>0.007325348721515</v>
       </c>
       <c r="G25" t="n">
-        <v>0.000145458557245453</v>
+        <v>0.000119688594305</v>
       </c>
       <c r="H25" t="n">
-        <v>0.007258548466475288</v>
+        <v>0.006349186668053</v>
       </c>
       <c r="I25" t="n">
-        <v>0.009399480220949516</v>
+        <v>0.007474822992653</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0004442644614519767</v>
+        <v>0.0003623206834181</v>
       </c>
       <c r="K25" t="n">
-        <v>0.013061973368652</v>
+        <v>0.0116305293046029</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="n">
-        <v>0.0009973084747489653</v>
-      </c>
+      <c r="E26" t="n">
+        <v>0.0006425771149646283</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="n">
-        <v>4.648442433065776e-08</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.0001699251079800581</v>
-      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>0.005467751871113469</v>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -1116,17 +1110,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="n">
-        <v>0.006921415161638838</v>
-      </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>0.002659399754462571</v>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -1137,55 +1131,69 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2050</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+        <v>2040</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.0005010576921071216</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.007604542097476213</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.01054764215702804</v>
+      </c>
       <c r="F29" t="n">
-        <v>2.224605818096596e-09</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+        <v>0.009567611865459695</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.000145458557245453</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.007258548466475288</v>
+      </c>
       <c r="I29" t="n">
-        <v>9.42629222471956e-10</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+        <v>0.009399480220949516</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.0004442644614519767</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.013061973368652</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2050</v>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="C30" t="n">
+        <v>0.0004895005497719998</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.0005471867918716412</v>
+      </c>
       <c r="E30" t="n">
-        <v>0.002197953337008217</v>
-      </c>
-      <c r="F30" t="n">
-        <v>8.942595679751571e-06</v>
-      </c>
+        <v>0.000799317559580526</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="n">
-        <v>6.633923700628604e-06</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1195,12 +1203,14 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>1.816557443737047e-05</v>
+        <v>0.0009973084747489653</v>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>4.648442433065776e-08</v>
+      </c>
       <c r="I31" t="n">
-        <v>2.158302253128147e-05</v>
+        <v>0.0001699251079800581</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1208,7 +1218,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1217,60 +1227,38 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
-        <v>7.754728230570779e-12</v>
-      </c>
-      <c r="G32" t="n">
-        <v>9.489684494844959e-13</v>
-      </c>
-      <c r="H32" t="n">
-        <v>3.428120915942979e-11</v>
-      </c>
-      <c r="I32" t="n">
-        <v>2.827298990628413e-11</v>
-      </c>
-      <c r="J32" t="n">
-        <v>5.612186533637588e-13</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1.088496491017329e-10</v>
-      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>2050</v>
       </c>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>0.006921415161638838</v>
+      </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
-        <v>0.0001213535326567438</v>
-      </c>
-      <c r="G33" t="n">
-        <v>4.604639930543995e-05</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.001202549676586484</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.0004488562716203</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.0001053926747668</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.0020320418553158</v>
-      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1280,28 +1268,20 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>0.0004892418401882201</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.0001079540432089</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.0057176896227644</v>
-      </c>
+        <v>2.224605818096596e-09</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.0013237224787817</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.0003118678534556</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.010784457730426</v>
-      </c>
+        <v>9.42629222471956e-10</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1310,19 +1290,23 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>0.0006229032602935643</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
+        <v>0.002197953337008217</v>
+      </c>
+      <c r="F35" t="n">
+        <v>8.942595679751571e-06</v>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>6.633923700628604e-06</v>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1330,48 +1314,206 @@
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="n">
-        <v>0.006167135529215985</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>1.816557443737047e-05</v>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>2.158302253128147e-05</v>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>2050</v>
       </c>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="n">
-        <v>0.006921415161638838</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.008987992126517765</v>
-      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
+        <v>7.754728230570779e-12</v>
+      </c>
+      <c r="G37" t="n">
+        <v>9.489684494844959e-13</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3.428120915942979e-11</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.827298990628413e-11</v>
+      </c>
+      <c r="J37" t="n">
+        <v>5.612186533637588e-13</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.088496491017329e-10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Biogenic Liquids</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>0.0001213535326567438</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4.604639930543995e-05</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.001202549676586484</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.0004488562716203</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.0001053926747668</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.0020320418553158</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Fossil Liquids</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>0.0004892418401882201</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.0001079540432089</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.0057176896227644</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.0013237224787817</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.0003118678534556</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.010784457730426</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Biomass [Solid]</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>0.0006229032602935643</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Fossil Rest</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Renewable Energy Carrier</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>0.006167135529215985</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Overall Demand</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.0004895005497719998</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.007468601953510479</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.009787309686098292</v>
+      </c>
+      <c r="F43" t="n">
         <v>0.001635014250071598</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G43" t="n">
         <v>0.0001540004434633084</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H43" t="n">
         <v>0.006920285818056424</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I43" t="n">
         <v>0.00197072177551618</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J43" t="n">
         <v>0.0004172605287836186</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K43" t="n">
         <v>0.01281649969459145</v>
       </c>
     </row>

--- a/Outputs/PtX_demand_HR.xlsx
+++ b/Outputs/PtX_demand_HR.xlsx
@@ -503,11 +503,19 @@
       <c r="E2" t="n">
         <v>0.0007836259586892497</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.003293061883258307</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.00064011970913</v>
+      </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>0.001137940541329</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0006112640170326</v>
+      </c>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -726,7 +734,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -735,7 +743,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>0.0006539468626333447</v>
+        <v>0.009016695477754882</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -747,7 +755,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -756,7 +764,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.009016695477754882</v>
+        <v>0.0006539468626333447</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -805,19 +813,19 @@
         <v>0.01145612335216135</v>
       </c>
       <c r="F15" t="n">
-        <v>0.03030065694914777</v>
+        <v>0.03359371883240608</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0001271406625798332</v>
+        <v>0.0007672603717098332</v>
       </c>
       <c r="H15" t="n">
         <v>0.007469376098141392</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0192962524219816</v>
+        <v>0.0204341929633106</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0004757422642456062</v>
+        <v>0.001087006281278206</v>
       </c>
       <c r="K15" t="n">
         <v>0.01329400971635877</v>
@@ -841,11 +849,19 @@
       <c r="E16" t="n">
         <v>0.0007921452568742928</v>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0.009356142887201364</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0007512395211245</v>
+      </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>0.0040216559867663</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.0006028483708596999</v>
+      </c>
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1068,7 +1084,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1077,7 +1093,7 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>0.0006425771149646283</v>
+        <v>0.005467751871113469</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
@@ -1089,7 +1105,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1098,7 +1114,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>0.005467751871113469</v>
+        <v>0.0006425771149646283</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
@@ -1147,19 +1163,19 @@
         <v>0.01054764215702804</v>
       </c>
       <c r="F29" t="n">
-        <v>0.009567611865459695</v>
+        <v>0.01892375475266106</v>
       </c>
       <c r="G29" t="n">
-        <v>0.000145458557245453</v>
+        <v>0.000896698078369953</v>
       </c>
       <c r="H29" t="n">
         <v>0.007258548466475288</v>
       </c>
       <c r="I29" t="n">
-        <v>0.009399480220949516</v>
+        <v>0.01342113620771582</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0004442644614519767</v>
+        <v>0.001047112832311677</v>
       </c>
       <c r="K29" t="n">
         <v>0.013061973368652</v>
@@ -1183,11 +1199,19 @@
       <c r="E30" t="n">
         <v>0.000799317559580526</v>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0.01089401565187417</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.0008436375915979</v>
+      </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>0.006052965642765</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.0006157035461158</v>
+      </c>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1422,7 +1446,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1430,9 +1454,7 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="n">
-        <v>0.0006229032602935643</v>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
@@ -1443,7 +1465,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1451,7 +1473,9 @@
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>0.0006229032602935643</v>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -1499,19 +1523,19 @@
         <v>0.009787309686098292</v>
       </c>
       <c r="F43" t="n">
-        <v>0.001635014250071598</v>
+        <v>0.01252902990194577</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0001540004434633084</v>
+        <v>0.0009976380350612084</v>
       </c>
       <c r="H43" t="n">
         <v>0.006920285818056424</v>
       </c>
       <c r="I43" t="n">
-        <v>0.00197072177551618</v>
+        <v>0.00802368741828118</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0004172605287836186</v>
+        <v>0.001032964074899419</v>
       </c>
       <c r="K43" t="n">
         <v>0.01281649969459145</v>
